--- a/转录数据/指标计算/统计指标-new.xlsx
+++ b/转录数据/指标计算/统计指标-new.xlsx
@@ -38,25 +38,25 @@
     <t>总体-名词-MRR</t>
   </si>
   <si>
+    <t>总体-自由量词-MRR</t>
+  </si>
+  <si>
+    <t>总体-自由名词-MRR</t>
+  </si>
+  <si>
     <t>总体-量词-accuracy</t>
   </si>
   <si>
     <t>总体-名词-accuracy</t>
   </si>
   <si>
+    <t>总体-自由量词-accuracy</t>
+  </si>
+  <si>
+    <t>总体-自由名词-accuracy</t>
+  </si>
+  <si>
     <t>总体-名词-bleu</t>
-  </si>
-  <si>
-    <t>总体-自由量词-MRR</t>
-  </si>
-  <si>
-    <t>总体-自由量词-accuracy</t>
-  </si>
-  <si>
-    <t>总体-自由名词-MRR</t>
-  </si>
-  <si>
-    <t>总体-自由名词-accuracy</t>
   </si>
   <si>
     <t>总体-自由-bleu</t>
@@ -1255,14 +1255,12 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6666666666667" style="2" customWidth="1"/>
-    <col min="2" max="3" width="16.8888888888889" style="2" customWidth="1"/>
-    <col min="4" max="5" width="23.1111111111111" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.1111111111111" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.8888888888889" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.1111111111111" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.8888888888889" style="2" customWidth="1"/>
-    <col min="10" max="10" width="28.1111111111111" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.1111111111111" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.8888888888889" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13" style="2" customWidth="1"/>
+    <col min="4" max="5" width="21.8888888888889" style="2" customWidth="1"/>
+    <col min="6" max="7" width="23.1111111111111" style="2" customWidth="1"/>
+    <col min="8" max="9" width="28.1111111111111" style="2" customWidth="1"/>
+    <col min="10" max="11" width="18.1111111111111" style="2" customWidth="1"/>
     <col min="12" max="12" width="16.8888888888889" style="2" customWidth="1"/>
     <col min="13" max="13" width="21.8888888888889" style="2" customWidth="1"/>
   </cols>
@@ -1319,25 +1317,25 @@
         <v>0.816667</v>
       </c>
       <c r="D2">
+        <v>0.880556</v>
+      </c>
+      <c r="E2">
+        <v>0.844444</v>
+      </c>
+      <c r="F2">
         <v>0.911111</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>0.675</v>
-      </c>
-      <c r="F2">
-        <v>0.927456</v>
-      </c>
-      <c r="G2">
-        <v>0.880556</v>
       </c>
       <c r="H2">
         <v>0.916667</v>
       </c>
       <c r="I2">
-        <v>0.844444</v>
+        <v>0.733333</v>
       </c>
       <c r="J2">
-        <v>0.733333</v>
+        <v>0.927456</v>
       </c>
       <c r="K2">
         <v>0.889133</v>
@@ -1360,25 +1358,25 @@
         <v>0.830556</v>
       </c>
       <c r="D3">
+        <v>0.715278</v>
+      </c>
+      <c r="E3">
+        <v>0.85</v>
+      </c>
+      <c r="F3">
         <v>0.905556</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>0.7</v>
-      </c>
-      <c r="F3">
-        <v>0.95057</v>
-      </c>
-      <c r="G3">
-        <v>0.715278</v>
       </c>
       <c r="H3">
         <v>0.85</v>
       </c>
       <c r="I3">
-        <v>0.85</v>
+        <v>0.733333</v>
       </c>
       <c r="J3">
-        <v>0.733333</v>
+        <v>0.95057</v>
       </c>
       <c r="K3">
         <v>0.889346</v>
@@ -1401,25 +1399,25 @@
         <v>0.809722</v>
       </c>
       <c r="D4">
+        <v>0.911111</v>
+      </c>
+      <c r="E4">
+        <v>0.827778</v>
+      </c>
+      <c r="F4">
         <v>0.916667</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>0.675</v>
-      </c>
-      <c r="F4">
-        <v>0.946708</v>
-      </c>
-      <c r="G4">
-        <v>0.911111</v>
       </c>
       <c r="H4">
         <v>0.95</v>
       </c>
       <c r="I4">
-        <v>0.827778</v>
+        <v>0.716667</v>
       </c>
       <c r="J4">
-        <v>0.716667</v>
+        <v>0.946708</v>
       </c>
       <c r="K4">
         <v>0.938028</v>
@@ -1442,25 +1440,25 @@
         <v>0.834722</v>
       </c>
       <c r="D5">
+        <v>0.784722</v>
+      </c>
+      <c r="E5">
+        <v>0.838889</v>
+      </c>
+      <c r="F5">
         <v>0.888889</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>0.691667</v>
-      </c>
-      <c r="F5">
-        <v>0.935295</v>
-      </c>
-      <c r="G5">
-        <v>0.784722</v>
       </c>
       <c r="H5">
         <v>0.883333</v>
       </c>
       <c r="I5">
-        <v>0.838889</v>
+        <v>0.7</v>
       </c>
       <c r="J5">
-        <v>0.7</v>
+        <v>0.935295</v>
       </c>
       <c r="K5">
         <v>0.892006</v>
@@ -1483,25 +1481,25 @@
         <v>0.795833</v>
       </c>
       <c r="D6">
+        <v>0.819444</v>
+      </c>
+      <c r="E6">
+        <v>0.761111</v>
+      </c>
+      <c r="F6">
         <v>0.927778</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>0.641667</v>
-      </c>
-      <c r="F6">
-        <v>0.904456</v>
-      </c>
-      <c r="G6">
-        <v>0.819444</v>
       </c>
       <c r="H6">
         <v>0.85</v>
       </c>
       <c r="I6">
-        <v>0.761111</v>
+        <v>0.616667</v>
       </c>
       <c r="J6">
-        <v>0.616667</v>
+        <v>0.904456</v>
       </c>
       <c r="K6">
         <v>0.881513</v>
@@ -1524,25 +1522,25 @@
         <v>0.822222</v>
       </c>
       <c r="D7">
+        <v>0.790278</v>
+      </c>
+      <c r="E7">
+        <v>0.872222</v>
+      </c>
+      <c r="F7">
         <v>0.905556</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0.683333</v>
-      </c>
-      <c r="F7">
-        <v>0.853504</v>
-      </c>
-      <c r="G7">
-        <v>0.790278</v>
       </c>
       <c r="H7">
         <v>0.866667</v>
       </c>
       <c r="I7">
-        <v>0.872222</v>
+        <v>0.766667</v>
       </c>
       <c r="J7">
-        <v>0.766667</v>
+        <v>0.853504</v>
       </c>
       <c r="K7">
         <v>0.911653</v>
@@ -1565,25 +1563,25 @@
         <v>0.818056</v>
       </c>
       <c r="D8">
+        <v>0.747222</v>
+      </c>
+      <c r="E8">
+        <v>0.822222</v>
+      </c>
+      <c r="F8">
         <v>0.883333</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>0.691667</v>
-      </c>
-      <c r="F8">
-        <v>0.920547</v>
-      </c>
-      <c r="G8">
-        <v>0.747222</v>
       </c>
       <c r="H8">
         <v>0.866667</v>
       </c>
       <c r="I8">
-        <v>0.822222</v>
+        <v>0.716667</v>
       </c>
       <c r="J8">
-        <v>0.716667</v>
+        <v>0.920547</v>
       </c>
       <c r="K8">
         <v>0.857754</v>
@@ -1606,25 +1604,25 @@
         <v>0.858333</v>
       </c>
       <c r="D9">
+        <v>0.7625</v>
+      </c>
+      <c r="E9">
+        <v>0.866667</v>
+      </c>
+      <c r="F9">
         <v>0.9</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>0.75</v>
-      </c>
-      <c r="F9">
-        <v>0.915975</v>
-      </c>
-      <c r="G9">
-        <v>0.7625</v>
       </c>
       <c r="H9">
         <v>0.883333</v>
       </c>
       <c r="I9">
-        <v>0.866667</v>
+        <v>0.766667</v>
       </c>
       <c r="J9">
-        <v>0.766667</v>
+        <v>0.915975</v>
       </c>
       <c r="K9">
         <v>0.904011</v>
